--- a/backend/backend test/backend_test_results.xlsx
+++ b/backend/backend test/backend_test_results.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.96</v>
+        <v>3.31</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>2.91</v>
+        <v>1.08</v>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.39</v>
+        <v>1.43</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>2.94</v>
+        <v>2.05</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.92</v>
+        <v>1</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.62</v>
+        <v>3.16</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2.91</v>
+        <v>2.71</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.15</v>
+        <v>3.14</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1.98</v>
+        <v>1.07</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>3.44</v>
+        <v>1.43</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.69</v>
+        <v>2.42</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2.17</v>
+        <v>1.28</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2.27</v>
+        <v>1.54</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2.29</v>
+        <v>3.42</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.77</v>
+        <v>0.89</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.91</v>
+        <v>1.21</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.74</v>
+        <v>3.44</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>3.14</v>
+        <v>2.32</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.95</v>
+        <v>3.42</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1.03</v>
+        <v>2.35</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>1.6</v>
+        <v>2.51</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2.79</v>
+        <v>0.95</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1.64</v>
+        <v>2.82</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>3.06</v>
+        <v>2.2</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.97</v>
+        <v>2.39</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.43</v>
+        <v>2.49</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2.68</v>
+        <v>2.31</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>3.01</v>
+        <v>2.44</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3.3</v>
+        <v>1.77</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2.76</v>
+        <v>0.95</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>2.47</v>
+        <v>3.27</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>1.24</v>
+        <v>2.35</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2.69</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2.81</v>
+        <v>1.04</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>3.26</v>
+        <v>0.86</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2.77</v>
+        <v>2.02</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2.86</v>
+        <v>1.67</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>1.1</v>
+        <v>1.86</v>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1.33</v>
+        <v>2.42</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.86</v>
+        <v>2.4</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>3.13</v>
+        <v>2.71</v>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1.63</v>
+        <v>0.92</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>3.16</v>
+        <v>3.33</v>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>3.15</v>
+        <v>2.36</v>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>2.98</v>
+        <v>3.44</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>3.04</v>
+        <v>1.7</v>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>2.67</v>
+        <v>2.03</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>3.06</v>
+        <v>1.33</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>2.48</v>
+        <v>0.86</v>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>3.27</v>
+        <v>1.56</v>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>3.29</v>
+        <v>1.76</v>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>2.9</v>
+        <v>1.13</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>2.51</v>
+        <v>1.72</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>3.29</v>
+        <v>1.35</v>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3.26</v>
+        <v>2.26</v>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>3.29</v>
+        <v>1.18</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1.31</v>
+        <v>2.93</v>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>2.68</v>
+        <v>3.16</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>3.18</v>
+        <v>1.15</v>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>1.6</v>
+        <v>3.34</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3.44</v>
+        <v>1.19</v>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1.58</v>
+        <v>2.93</v>
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1.68</v>
+        <v>2.59</v>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>1.41</v>
+        <v>0.87</v>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="G97" s="5" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>1.07</v>
+        <v>1.58</v>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>2.55</v>
+        <v>3.44</v>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>2.74</v>
+        <v>2.17</v>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>2.91</v>
+        <v>2.04</v>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>3.21</v>
+        <v>0.87</v>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>3.33</v>
+        <v>1.21</v>
       </c>
       <c r="H115" s="6" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>2.91</v>
+        <v>1.41</v>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="G117" s="5" t="n">
-        <v>2.31</v>
+        <v>3.41</v>
       </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>1.39</v>
+        <v>2.76</v>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H119" s="6" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="H121" s="6" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.97</v>
+        <v>2.61</v>
       </c>
       <c r="H123" s="6" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>2.13</v>
+        <v>3.17</v>
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>3.31</v>
+        <v>2.96</v>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>1.61</v>
+        <v>3.24</v>
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>2.77</v>
+        <v>1.12</v>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="H129" s="6" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>2.71</v>
+        <v>3.38</v>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>2.99</v>
+        <v>1.24</v>
       </c>
       <c r="H131" s="6" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="H133" s="6" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>2.72</v>
+        <v>1.09</v>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>2.01</v>
+        <v>3.43</v>
       </c>
       <c r="H135" s="6" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2.46</v>
+        <v>3.42</v>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="G137" s="5" t="n">
-        <v>1.14</v>
+        <v>2.86</v>
       </c>
       <c r="H137" s="6" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>2.55</v>
+        <v>2.24</v>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>2.41</v>
+        <v>2.19</v>
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>1.57</v>
+        <v>2.56</v>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1.18</v>
+        <v>3.38</v>
       </c>
       <c r="H141" s="6" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1.36</v>
+        <v>2.79</v>
       </c>
       <c r="H143" s="6" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>3.2</v>
+        <v>2.07</v>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>2.49</v>
+        <v>1.53</v>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>3.38</v>
+        <v>2.17</v>
       </c>
       <c r="H147" s="6" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>2.89</v>
+        <v>1.36</v>
       </c>
       <c r="H153" s="6" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>1.44</v>
+        <v>2.79</v>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>3.24</v>
+        <v>0.97</v>
       </c>
       <c r="H155" s="6" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1.12</v>
+        <v>1.84</v>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>2.19</v>
+        <v>1.01</v>
       </c>
       <c r="H157" s="6" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>3.44</v>
+        <v>2.87</v>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1.28</v>
+        <v>3.27</v>
       </c>
       <c r="H159" s="6" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1.92</v>
+        <v>3.26</v>
       </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>1.52</v>
+        <v>2.83</v>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>3.37</v>
+        <v>1.39</v>
       </c>
       <c r="H163" s="6" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1.21</v>
+        <v>2.16</v>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="G168" s="2" t="n">
-        <v>3.43</v>
+        <v>2.54</v>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>2.25</v>
+        <v>0.91</v>
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>2.24</v>
+        <v>1.35</v>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>2.52</v>
+        <v>1.32</v>
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>2.75</v>
+        <v>1.31</v>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="H177" s="6" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>0.91</v>
+        <v>2.84</v>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>1.4</v>
+        <v>3.18</v>
       </c>
       <c r="H181" s="6" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="G184" s="2" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="H185" s="6" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="G186" s="2" t="n">
-        <v>2.14</v>
+        <v>2.64</v>
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="H187" s="6" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>0.92</v>
+        <v>2.04</v>
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2.64</v>
+        <v>1.09</v>
       </c>
       <c r="H189" s="6" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="H191" s="6" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>3.3</v>
+        <v>2.43</v>
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="H193" s="6" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2.61</v>
+        <v>1.43</v>
       </c>
       <c r="H197" s="6" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="H198" s="3" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>1.19</v>
+        <v>0.87</v>
       </c>
       <c r="H199" s="6" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2.63</v>
+        <v>1.17</v>
       </c>
       <c r="H201" s="6" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2.94</v>
+        <v>3.14</v>
       </c>
       <c r="H203" s="6" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="G204" s="2" t="n">
-        <v>2.86</v>
+        <v>3.06</v>
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>1.78</v>
+        <v>3.17</v>
       </c>
       <c r="H205" s="6" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="G206" s="2" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>2.79</v>
+        <v>3.16</v>
       </c>
       <c r="H207" s="6" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="G208" s="2" t="n">
-        <v>2.01</v>
+        <v>3.25</v>
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="H209" s="6" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="G210" s="2" t="n">
-        <v>0.96</v>
+        <v>1.76</v>
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>3.19</v>
+        <v>2.21</v>
       </c>
       <c r="H211" s="6" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="G212" s="2" t="n">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="H213" s="6" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="G214" s="2" t="n">
-        <v>3.32</v>
+        <v>3.01</v>
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>2.96</v>
+        <v>1.77</v>
       </c>
       <c r="H215" s="6" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="G216" s="2" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="H217" s="6" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="G218" s="2" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>2.62</v>
+        <v>3.12</v>
       </c>
       <c r="H219" s="6" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="G220" s="2" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="H221" s="6" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="G222" s="2" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9711,7 @@
         </is>
       </c>
       <c r="G224" s="2" t="n">
-        <v>3.23</v>
+        <v>2.74</v>
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>2.88</v>
+        <v>1.27</v>
       </c>
       <c r="H225" s="6" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
         </is>
       </c>
       <c r="G226" s="2" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="H227" s="6" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="G228" s="2" t="n">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>3.33</v>
+        <v>1.08</v>
       </c>
       <c r="H229" s="6" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9957,7 +9957,7 @@
         </is>
       </c>
       <c r="G230" s="2" t="n">
-        <v>2.43</v>
+        <v>3.37</v>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="H231" s="6" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
         </is>
       </c>
       <c r="G232" s="2" t="n">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="H233" s="6" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="G234" s="2" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10162,7 +10162,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>2.51</v>
+        <v>1.15</v>
       </c>
       <c r="H235" s="6" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="G236" s="2" t="n">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>3.43</v>
+        <v>1.88</v>
       </c>
       <c r="H237" s="6" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="G238" s="2" t="n">
-        <v>2.13</v>
+        <v>1.29</v>
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10326,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>2.96</v>
+        <v>3.44</v>
       </c>
       <c r="H239" s="6" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10367,7 @@
         </is>
       </c>
       <c r="G240" s="2" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1.12</v>
+        <v>2.59</v>
       </c>
       <c r="H241" s="6" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="G242" s="2" t="n">
-        <v>1.65</v>
+        <v>3.33</v>
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>2.81</v>
+        <v>1.11</v>
       </c>
       <c r="H243" s="6" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10531,7 @@
         </is>
       </c>
       <c r="G244" s="2" t="n">
-        <v>3.25</v>
+        <v>2.24</v>
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>2.67</v>
+        <v>2.23</v>
       </c>
       <c r="H245" s="6" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
         </is>
       </c>
       <c r="G246" s="2" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2.88</v>
+        <v>1.37</v>
       </c>
       <c r="H247" s="6" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="G248" s="2" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>1.51</v>
+        <v>2.8</v>
       </c>
       <c r="H249" s="6" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="G250" s="2" t="n">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="H250" s="3" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>1.83</v>
+        <v>3.37</v>
       </c>
       <c r="H251" s="6" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
       </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
         </is>
       </c>
       <c r="G252" s="2" t="n">
-        <v>2.89</v>
+        <v>1.42</v>
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="H253" s="6" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
         </is>
       </c>
       <c r="G254" s="2" t="n">
-        <v>0.99</v>
+        <v>2.18</v>
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>1.64</v>
+        <v>1.03</v>
       </c>
       <c r="H255" s="6" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11023,7 +11023,7 @@
         </is>
       </c>
       <c r="G256" s="2" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="H256" s="3" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="H257" s="6" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="G258" s="2" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2.47</v>
+        <v>3.39</v>
       </c>
       <c r="H259" s="6" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="G260" s="2" t="n">
-        <v>1.36</v>
+        <v>2.16</v>
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>1.99</v>
+        <v>1.49</v>
       </c>
       <c r="H261" s="6" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>1.01</v>
+        <v>2.47</v>
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="H263" s="6" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11351,7 @@
         </is>
       </c>
       <c r="G264" s="2" t="n">
-        <v>1.82</v>
+        <v>1.06</v>
       </c>
       <c r="H264" s="3" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="H265" s="6" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
       </c>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.89</v>
+        <v>3.42</v>
       </c>
       <c r="H266" s="3" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2.4</v>
+        <v>1.23</v>
       </c>
       <c r="H267" s="6" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="G268" s="2" t="n">
-        <v>2.05</v>
+        <v>2.99</v>
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="H269" s="6" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11597,7 @@
         </is>
       </c>
       <c r="G270" s="2" t="n">
-        <v>2.05</v>
+        <v>1.04</v>
       </c>
       <c r="H270" s="3" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="G271" s="5" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="H271" s="6" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="G272" s="2" t="n">
-        <v>2.48</v>
+        <v>1.3</v>
       </c>
       <c r="H272" s="3" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="H273" s="6" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
         </is>
       </c>
       <c r="G274" s="2" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="G275" s="5" t="n">
-        <v>3.06</v>
+        <v>2.62</v>
       </c>
       <c r="H275" s="6" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="G276" s="2" t="n">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="H276" s="3" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>2.24</v>
+        <v>3.18</v>
       </c>
       <c r="H277" s="6" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="G278" s="2" t="n">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
         </is>
       </c>
       <c r="G279" s="5" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="H279" s="6" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12007,7 +12007,7 @@
         </is>
       </c>
       <c r="G280" s="2" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12048,7 +12048,7 @@
         </is>
       </c>
       <c r="G281" s="5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="H281" s="6" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>2.58</v>
+        <v>3.14</v>
       </c>
       <c r="H282" s="3" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="G283" s="5" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="H283" s="6" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="G284" s="2" t="n">
-        <v>1.15</v>
+        <v>3.28</v>
       </c>
       <c r="H284" s="3" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
         </is>
       </c>
       <c r="G285" s="5" t="n">
-        <v>0.85</v>
+        <v>3.18</v>
       </c>
       <c r="H285" s="6" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="G286" s="2" t="n">
-        <v>2.63</v>
+        <v>1.27</v>
       </c>
       <c r="H286" s="3" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
         </is>
       </c>
       <c r="G287" s="5" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="H287" s="6" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="G288" s="2" t="n">
-        <v>1.79</v>
+        <v>0.92</v>
       </c>
       <c r="H288" s="3" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12376,7 @@
         </is>
       </c>
       <c r="G289" s="5" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="H289" s="6" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
         </is>
       </c>
       <c r="G290" s="2" t="n">
-        <v>1.35</v>
+        <v>3.1</v>
       </c>
       <c r="H290" s="3" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
         </is>
       </c>
       <c r="G291" s="5" t="n">
-        <v>2.52</v>
+        <v>1.63</v>
       </c>
       <c r="H291" s="6" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="G292" s="2" t="n">
-        <v>1.49</v>
+        <v>2.09</v>
       </c>
       <c r="H292" s="3" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="G293" s="5" t="n">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="H293" s="6" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="G294" s="2" t="n">
-        <v>0.9</v>
+        <v>2.91</v>
       </c>
       <c r="H294" s="3" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
         </is>
       </c>
       <c r="G295" s="5" t="n">
-        <v>3.23</v>
+        <v>1.31</v>
       </c>
       <c r="H295" s="6" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12663,7 +12663,7 @@
         </is>
       </c>
       <c r="G296" s="2" t="n">
-        <v>1.79</v>
+        <v>2.92</v>
       </c>
       <c r="H296" s="3" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12704,7 +12704,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="H297" s="6" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
       </c>
       <c r="I297" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="G298" s="2" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="H298" s="3" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12786,7 +12786,7 @@
         </is>
       </c>
       <c r="G299" s="5" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="H299" s="6" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="I299" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="G300" s="2" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="H300" s="3" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="G301" s="5" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="H301" s="6" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="I301" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01 13:16:11</t>
+          <t>2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
@@ -12909,7 +12909,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Execution Date: 2026-08-01 13:16:12</t>
+          <t>Execution Date: 2026-08-01 13:37:06</t>
         </is>
       </c>
     </row>
